--- a/output/roomself_excel/8026.xlsx
+++ b/output/roomself_excel/8026.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>312352</v>
+        <v>121644</v>
       </c>
       <c r="D2" t="n">
-        <v>5612</v>
+        <v>2796</v>
       </c>
       <c r="E2" t="n">
-        <v>1074</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>573</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>151728</v>
+        <v>255414</v>
       </c>
       <c r="D3" t="n">
-        <v>3164</v>
+        <v>4240</v>
       </c>
       <c r="E3" t="n">
-        <v>327</v>
+        <v>730</v>
       </c>
       <c r="F3" t="n">
-        <v>21</v>
+        <v>573</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>121644</v>
+        <v>151728</v>
       </c>
       <c r="D4" t="n">
-        <v>2796</v>
+        <v>3164</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>327</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
@@ -546,6 +546,28 @@
       </c>
       <c r="F5" t="n">
         <v>21</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Hallway</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>56938</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2036</v>
+      </c>
+      <c r="E6" t="n">
+        <v>344</v>
+      </c>
+      <c r="F6" t="n">
+        <v>187</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/8026.xlsx
+++ b/output/roomself_excel/8026.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,12 +495,20 @@
       <c r="D2" t="n">
         <v>2796</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
-      </c>
+        <v>372</v>
+      </c>
+      <c r="G2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,11 +525,27 @@
       <c r="D3" t="n">
         <v>4240</v>
       </c>
-      <c r="E3" t="n">
-        <v>730</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>573</v>
+        <v>555</v>
+      </c>
+      <c r="G3" t="n">
+        <v>21</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>663</v>
+      </c>
+      <c r="J3" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="4">
@@ -519,11 +563,27 @@
       <c r="D4" t="n">
         <v>3164</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>327</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>21</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>464</v>
+      </c>
+      <c r="J4" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -541,10 +601,26 @@
       <c r="D5" t="n">
         <v>2004</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>174</v>
+      </c>
+      <c r="G5" t="n">
+        <v>20</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>327</v>
       </c>
-      <c r="F5" t="n">
+      <c r="J5" t="n">
         <v>21</v>
       </c>
     </row>
@@ -563,11 +639,27 @@
       <c r="D6" t="n">
         <v>2036</v>
       </c>
-      <c r="E6" t="n">
-        <v>344</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>187</v>
+        <v>323</v>
+      </c>
+      <c r="G6" t="n">
+        <v>21</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>166</v>
+      </c>
+      <c r="J6" t="n">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
